--- a/outputs/16511.xlsx
+++ b/outputs/16511.xlsx
@@ -143,16 +143,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -351,125 +355,125 @@
   <dimension ref="D1:F10"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D2,D2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D3,D3)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D4,D4)</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D5,D5)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D6,D6)</f>
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D7,D7)</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D8,D8)</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D9,D9)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <f aca="false">COUNTIF($D$2:D10,D10)</f>
         <v>3</v>
       </c>
